--- a/roster.xlsx
+++ b/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdalsanto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdalsanto\Desktop\linkgenerators\newsdesk roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152407A6-1E9D-4DCD-9B80-85599747BB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA3D4567-74CB-4681-8A15-AFDE963ED2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,12 @@
     <sheet name="Sat" sheetId="7" r:id="rId7"/>
     <sheet name="Sun" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="49">
   <si>
     <t>EBS Newsdesk — weekly roster template (v4)</t>
   </si>
@@ -183,16 +183,45 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000099"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000099"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -200,82 +229,31 @@
       <sz val="16"/>
       <color rgb="FF000099"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000099"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF888888"/>
-      <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000099"/>
       <name val="Arial"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000099"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000099"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,61 +262,47 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3B0"/>
-        <bgColor rgb="FFFFF4D6"/>
+        <fgColor rgb="FFEFF1F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000099"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAE6F2"/>
-        <bgColor rgb="FFE6ECFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4D6"/>
-        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE0CC"/>
-        <bgColor rgb="FFFFF4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6ECFF"/>
-        <bgColor rgb="FFEFF1F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE0E8E0"/>
-        <bgColor rgb="FFEAE6F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF1F8"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF000099"/>
-        <bgColor rgb="FF000080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFEFF1F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF4D6"/>
+        <fgColor rgb="FFFFF3B0"/>
       </patternFill>
     </fill>
   </fills>
@@ -366,139 +330,64 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{0401423D-8144-45BB-A318-8CE3753119F7}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000099"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFEAE6F2"/>
-      <rgbColor rgb="FF888888"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF4D6"/>
-      <rgbColor rgb="FFE6ECFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD0D0D0"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEFF1F8"/>
-      <rgbColor rgb="FFE0E8E0"/>
-      <rgbColor rgb="FFFFF3B0"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFE0CC"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -515,10 +404,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -556,128 +445,234 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -690,7 +685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -699,1964 +694,1958 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
+      <c r="A13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="24"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="23"/>
+    </row>
+    <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="24"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="24"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="24"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="24"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="24"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F18" s="24"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="24"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:F20" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="24"/>
+      <c r="B8" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="24"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="24"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="24"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="B17" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="24"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="24"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:F20" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>18</v>
-      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>18</v>
-      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="24"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="24"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="24"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:F20" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="24" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="24"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="24"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="24"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="23" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="24" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24" t="s">
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="24"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="24" t="s">
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="23" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="24"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:F20" xr:uid="{00000000-0002-0000-0400-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" xr:uid="{00000000-0002-0000-0400-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="24"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>18</v>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="24"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="24"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="24"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="24"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:F20" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="23"/>
+      <c r="B7" s="22"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="23"/>
+      <c r="B8" s="22"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="22"/>
     </row>
     <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="23"/>
+      <c r="B10" s="22"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="23"/>
+      <c r="B11" s="22"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="23"/>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="23"/>
+      <c r="B13" s="22"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="23"/>
+      <c r="B14" s="22"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="23"/>
+      <c r="B15" s="22"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="23"/>
+      <c r="B16" s="22"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="23"/>
+      <c r="B17" s="22"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="23"/>
+      <c r="B18" s="22"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="23"/>
+      <c r="B19" s="22"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="23"/>
+      <c r="B20" s="22"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="25"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
+      <c r="B24" s="25"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
+      <c r="B25" s="25"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:B20" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="23"/>
+      <c r="B7" s="22"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="23"/>
+      <c r="B8" s="22"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="22"/>
     </row>
     <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="23"/>
+      <c r="B10" s="22"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="23"/>
+      <c r="B11" s="22"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>18</v>
-      </c>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="23"/>
+      <c r="B13" s="22"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="23"/>
+      <c r="B14" s="22"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="23"/>
+      <c r="B15" s="22"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="23"/>
+      <c r="B16" s="22"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="23"/>
+      <c r="B17" s="22"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="23"/>
+      <c r="B18" s="22"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="23"/>
+      <c r="B19" s="22"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="23"/>
+      <c r="B20" s="22"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="25"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1"/>
+      <c r="B24" s="25"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="1"/>
+      <c r="B25" s="25"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B4:D4" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B4 C4 D4" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"Working,OFF,ON MISSION"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B7:B20" xr:uid="{00000000-0002-0000-0700-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>"Giovanni,Zoe,Claudio,"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdalsanto\Desktop\linkgenerators\newsdesk roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA3D4567-74CB-4681-8A15-AFDE963ED2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EEE928-49F9-4424-82DF-0CC173AE8ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="49">
   <si>
     <t>EBS Newsdesk — weekly roster template (v4)</t>
   </si>
@@ -2552,7 +2552,9 @@
       <c r="A12" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="22"/>
+      <c r="B12" s="22" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdalsanto\Desktop\linkgenerators\newsdesk roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EEE928-49F9-4424-82DF-0CC173AE8ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ABF94D-1C58-40B0-9DAD-C32562575C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="49">
   <si>
     <t>EBS Newsdesk — weekly roster template (v4)</t>
   </si>
@@ -922,9 +922,7 @@
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="s">
-        <v>17</v>
-      </c>
+      <c r="D13" s="21"/>
       <c r="E13" s="22" t="s">
         <v>17</v>
       </c>
@@ -2050,9 +2048,7 @@
       <c r="C8" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>17</v>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="22" t="s">
         <v>19</v>
       </c>
@@ -2066,16 +2062,14 @@
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>17</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
@@ -2095,9 +2089,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="20" t="s">
-        <v>17</v>
-      </c>
+      <c r="C11" s="20"/>
       <c r="D11" s="21"/>
       <c r="E11" s="22"/>
       <c r="F11" s="23" t="s">
@@ -2112,9 +2104,7 @@
       <c r="C12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>17</v>
-      </c>
+      <c r="D12" s="21"/>
       <c r="E12" s="22" t="s">
         <v>19</v>
       </c>
@@ -2169,12 +2159,8 @@
         <v>33</v>
       </c>
       <c r="B17" s="19"/>
-      <c r="C17" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>17</v>
-      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="22" t="s">
         <v>19</v>
       </c>
@@ -2202,9 +2188,7 @@
       <c r="C19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>17</v>
-      </c>
+      <c r="D19" s="21"/>
       <c r="E19" s="22" t="s">
         <v>17</v>
       </c>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdalsanto\Desktop\linkgenerators\newsdesk roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ABF94D-1C58-40B0-9DAD-C32562575C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E97454A3-A78F-485F-8A87-B617CCF9B420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="49">
   <si>
     <t>EBS Newsdesk — weekly roster template (v4)</t>
   </si>
@@ -35,9 +35,6 @@
     <t>WEEK STARTING (Monday):</t>
   </si>
   <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
     <t>← type the Monday date of the week you're publishing</t>
   </si>
   <si>
@@ -174,6 +171,9 @@
   </si>
   <si>
     <t>Sun (fallback block)</t>
+  </si>
+  <si>
+    <t>OFF</t>
   </si>
 </sst>
 </file>
@@ -702,56 +702,56 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="3">
+        <v>46202</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>2</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>5</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -759,22 +759,22 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -793,60 +793,60 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="20"/>
@@ -856,10 +856,12 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="20" t="s">
+        <v>17</v>
+      </c>
       <c r="D8" s="21"/>
       <c r="E8" s="22" t="s">
         <v>17</v>
@@ -868,11 +870,11 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="22" t="s">
@@ -882,11 +884,11 @@
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
@@ -896,10 +898,12 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="D11" s="21"/>
       <c r="E11" s="22" t="s">
         <v>18</v>
@@ -908,7 +912,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="20"/>
@@ -918,70 +922,62 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
       <c r="D13" s="21"/>
-      <c r="E13" s="22" t="s">
-        <v>17</v>
-      </c>
+      <c r="E13" s="22"/>
       <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
       <c r="D14" s="21"/>
-      <c r="E14" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="E14" s="22"/>
       <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19"/>
-      <c r="C15" s="20" t="s">
-        <v>18</v>
-      </c>
+      <c r="C15" s="20"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
       <c r="D16" s="21"/>
-      <c r="E16" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="E16" s="22"/>
       <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="20"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="E17" s="22"/>
       <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="19"/>
-      <c r="C18" s="20"/>
+      <c r="C18" s="20" t="s">
+        <v>17</v>
+      </c>
       <c r="D18" s="21"/>
       <c r="E18" s="22" t="s">
         <v>17</v>
@@ -990,36 +986,34 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="22" t="s">
-        <v>17</v>
-      </c>
+      <c r="E19" s="22"/>
       <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
+      <c r="C20" s="20" t="s">
+        <v>17</v>
+      </c>
       <c r="D20" s="21"/>
-      <c r="E20" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="E20" s="22"/>
       <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -1029,7 +1023,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -1039,7 +1033,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -1049,7 +1043,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -1087,102 +1081,98 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="19"/>
-      <c r="C7" s="20" t="s">
-        <v>19</v>
-      </c>
+      <c r="C7" s="20"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="E7" s="22"/>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>18</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B8" s="19"/>
       <c r="C8" s="20" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
+      <c r="E8" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
@@ -1190,25 +1180,27 @@
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="D11" s="21"/>
       <c r="E11" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="20"/>
@@ -1218,67 +1210,53 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>17</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="22"/>
       <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>18</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="21"/>
       <c r="E14" s="22"/>
       <c r="F14" s="23"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20"/>
       <c r="D15" s="21"/>
-      <c r="E15" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="E15" s="22"/>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
+      <c r="C16" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="D16" s="21"/>
       <c r="E16" s="22"/>
-      <c r="F16" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="F16" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>18</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B17" s="19"/>
       <c r="C17" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="22"/>
@@ -1286,33 +1264,33 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="21"/>
       <c r="E18" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20"/>
       <c r="D19" s="21"/>
       <c r="E19" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
@@ -1322,12 +1300,12 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -1337,7 +1315,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -1347,7 +1325,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -1357,7 +1335,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -1395,84 +1373,84 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="19"/>
-      <c r="C7" s="20" t="s">
-        <v>19</v>
-      </c>
+      <c r="C7" s="20"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="E7" s="22"/>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="20" t="s">
+        <v>17</v>
+      </c>
       <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
+      <c r="E8" s="22" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20" t="s">
@@ -1486,35 +1464,31 @@
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="21"/>
       <c r="E10" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="20" t="s">
-        <v>19</v>
-      </c>
+      <c r="C11" s="20"/>
       <c r="D11" s="21"/>
-      <c r="E11" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="E11" s="22"/>
       <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="20"/>
@@ -1524,7 +1498,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
@@ -1534,7 +1508,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
@@ -1544,21 +1518,17 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19"/>
-      <c r="C15" s="20" t="s">
-        <v>18</v>
-      </c>
+      <c r="C15" s="20"/>
       <c r="D15" s="21"/>
-      <c r="E15" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="E15" s="22"/>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
@@ -1568,7 +1538,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="20"/>
@@ -1578,19 +1548,21 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="19"/>
-      <c r="C18" s="20"/>
+      <c r="C18" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="D18" s="21"/>
       <c r="E18" s="22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20"/>
@@ -1600,24 +1572,24 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
       <c r="D20" s="21"/>
       <c r="E20" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -1627,7 +1599,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -1637,7 +1609,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -1647,7 +1619,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -1685,138 +1657,140 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
+      <c r="E7" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="19"/>
-      <c r="C8" s="20"/>
+      <c r="C8" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="D8" s="21"/>
       <c r="E8" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="22"/>
+        <v>17</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22" t="s">
+        <v>17</v>
+      </c>
       <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="19"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="E11" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="20"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
@@ -1826,7 +1800,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
@@ -1836,7 +1810,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20"/>
@@ -1846,7 +1820,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
@@ -1856,62 +1830,58 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="20"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="19"/>
-      <c r="C18" s="20"/>
+      <c r="C18" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="D18" s="21"/>
       <c r="E18" s="22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="20"/>
       <c r="D19" s="21"/>
       <c r="E19" s="22"/>
-      <c r="F19" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
       <c r="D20" s="21"/>
       <c r="E20" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -1921,7 +1891,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -1931,7 +1901,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -1941,7 +1911,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -1979,142 +1949,136 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
+      <c r="E7" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="21"/>
       <c r="E8" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>19</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="20" t="s">
-        <v>18</v>
-      </c>
+      <c r="C9" s="20"/>
       <c r="D9" s="21"/>
-      <c r="E9" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>19</v>
-      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
+      <c r="D10" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>16</v>
+      </c>
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="21"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="23" t="s">
-        <v>19</v>
-      </c>
+      <c r="E11" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="19"/>
-      <c r="C12" s="20" t="s">
-        <v>17</v>
-      </c>
+      <c r="C12" s="20"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>19</v>
-      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="20"/>
@@ -2124,7 +2088,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20"/>
@@ -2134,19 +2098,17 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19"/>
-      <c r="C15" s="20" t="s">
-        <v>18</v>
-      </c>
+      <c r="C15" s="20"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
       <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20"/>
@@ -2156,64 +2118,60 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="20"/>
       <c r="D17" s="21"/>
-      <c r="E17" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>19</v>
-      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="21"/>
-      <c r="E18" s="22"/>
+      <c r="E18" s="22" t="s">
+        <v>16</v>
+      </c>
       <c r="F18" s="23"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="19"/>
-      <c r="C19" s="20" t="s">
-        <v>17</v>
-      </c>
+      <c r="C19" s="20"/>
       <c r="D19" s="21"/>
       <c r="E19" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" s="23"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="20"/>
       <c r="D20" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="23"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -2223,7 +2181,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -2233,7 +2191,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -2243,7 +2201,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
@@ -2281,155 +2239,155 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="22"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="22"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="22"/>
     </row>
     <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="22"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="22"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="22"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="22"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="22"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="22"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="22"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="22"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="22"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="22"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
     </row>
@@ -2463,157 +2421,155 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="C4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="22"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="22"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="22"/>
     </row>
     <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="22"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="22"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>18</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B12" s="22"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="22"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="22"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" s="22"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="22"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B17" s="22"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="22"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="22"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" s="22"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="25"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="25"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="25"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="25"/>
     </row>

--- a/roster.xlsx
+++ b/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdalsanto\Desktop\linkgenerators\newsdesk roster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E97454A3-A78F-485F-8A87-B617CCF9B420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44659686-2E34-4E1B-9299-B8E2FDEFA0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="49">
   <si>
     <t>EBS Newsdesk — weekly roster template (v4)</t>
   </si>
@@ -1190,11 +1190,11 @@
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="23"/>
     </row>
@@ -1429,9 +1429,13 @@
         <v>22</v>
       </c>
       <c r="B7" s="19"/>
-      <c r="C7" s="20"/>
+      <c r="C7" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
+      <c r="E7" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
